--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90283</v>
+        <v>90286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90286</v>
+        <v>90289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90289</v>
+        <v>90293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90293</v>
+        <v>90300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90300</v>
+        <v>90302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92841</v>
+        <v>92843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90302</v>
+        <v>90303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92843</v>
+        <v>92829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92829</v>
+        <v>92830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90303</v>
+        <v>90306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90306</v>
+        <v>90308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90308</v>
+        <v>90312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90312</v>
+        <v>90313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49130-2025 artfynd.xlsx
+++ b/artfynd/A 49130-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129075774</v>
       </c>
       <c r="B3" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129075606</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129075633</v>
       </c>
       <c r="B5" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>129075567</v>
       </c>
       <c r="B6" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129075971</v>
       </c>
       <c r="B7" t="n">
-        <v>90313</v>
+        <v>90316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>129075710</v>
       </c>
       <c r="B8" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
